--- a/outputs/full_pipeline_results.xlsx
+++ b/outputs/full_pipeline_results.xlsx
@@ -7,9 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Classification" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="RUL_Prediction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Scheduling" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="All Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,359 +425,580 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>accuracy</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>f1</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>auc</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Logistic Regression</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.822</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.2393162393162393</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.9083774814273535</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Random Forest</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.9445</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.5066666666666667</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.9734121909633418</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.9705</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.6467065868263473</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.9708698696870053</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>BiLSTM</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.8865</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.3569405099150141</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.9562324929971988</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Hybrid XGBoost-LSTM (Proposed)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.9755</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.6878980891719745</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.9013822920472536</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>rmse</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>mae</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>r2</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>nasa_score</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>LSTM</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>13.17349207897008</v>
-      </c>
-      <c r="C2" t="n">
-        <v>10.04725551605225</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.8919332027435303</v>
-      </c>
-      <c r="E2" t="n">
-        <v>290.1172180175781</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>GRU</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>13.16151565682181</v>
-      </c>
-      <c r="C3" t="n">
-        <v>9.658679962158203</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.89212965965271</v>
-      </c>
-      <c r="E3" t="n">
-        <v>311.1829528808594</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>CNN-LSTM</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>12.97223750641544</v>
-      </c>
-      <c r="C4" t="n">
-        <v>9.51572322845459</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.8952099084854126</v>
-      </c>
-      <c r="E4" t="n">
-        <v>287.953125</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Attention-LSTM</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>13.61309462300339</v>
-      </c>
-      <c r="C5" t="n">
-        <v>9.904352188110352</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.8846004605293274</v>
-      </c>
-      <c r="E5" t="n">
-        <v>351.1046752929688</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>CNN-LSTM-Attention (Proposed)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>18.88697687582141</v>
-      </c>
-      <c r="C6" t="n">
-        <v>13.28687858581543</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.7778658866882324</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1131.293090820312</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Hybrid XGBoost-LSTM-Att. (Proposed)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>17.87770070834579</v>
-      </c>
-      <c r="C7" t="n">
-        <v>12.74594402313232</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.8009722232818604</v>
-      </c>
-      <c r="E7" t="n">
-        <v>886.8207397460938</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>pipeline</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>auc</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>rmse</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>mae</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>nasa_score</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>mean_reward</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>mean_failures</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>mean_tardiness</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>on_time_rate_%</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>downtime_%</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>schedule_stability_index</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Reactive + Static</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>-214.6752006512496</v>
+          <t>Logistic Regression</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>4.74</v>
+        <v>0.822</v>
       </c>
       <c r="D2" t="n">
-        <v>1673.518437283135</v>
-      </c>
+        <v>0.2393162393162393</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9083774814273535</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Predictive Maintenance Only</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>-124.4028082124057</v>
+          <t>Random Forest</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>0.43</v>
+        <v>0.9445</v>
       </c>
       <c r="D3" t="n">
-        <v>1757.172566591339</v>
-      </c>
+        <v>0.5066666666666667</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9734121909633418</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Scheduling Optimisation Only</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>-46.62122834805262</v>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>4.25</v>
+        <v>0.9705</v>
       </c>
       <c r="D4" t="n">
-        <v>201.0102362337719</v>
-      </c>
+        <v>0.6467065868263473</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9708698696870053</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
+          <t>BiLSTM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8685</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3168831168831169</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9541849348435026</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Hybrid XGBoost-LSTM (Proposed)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9055839727195225</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RUL_Prediction</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>13.19481293459313</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10.14827346801758</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.8915831446647644</v>
+      </c>
+      <c r="I7" t="n">
+        <v>286.8256225585938</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>GRU</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RUL_Prediction</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>13.17457098651455</v>
+      </c>
+      <c r="G8" t="n">
+        <v>9.598400115966797</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8919155597686768</v>
+      </c>
+      <c r="I8" t="n">
+        <v>310.8833312988281</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>CNN-LSTM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>RUL_Prediction</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>13.38269335086335</v>
+      </c>
+      <c r="G9" t="n">
+        <v>9.862846374511719</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.8884736895561218</v>
+      </c>
+      <c r="I9" t="n">
+        <v>311.1583251953125</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Attention-LSTM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>RUL_Prediction</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>14.9528183541899</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.98691654205322</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.8607688546180725</v>
+      </c>
+      <c r="I10" t="n">
+        <v>553.6170043945312</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>CNN-LSTM-Attention (Proposed)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>RUL_Prediction</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>18.27844028889039</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12.46864891052246</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.7919495701789856</v>
+      </c>
+      <c r="I11" t="n">
+        <v>996.0452270507812</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Hybrid XGBoost-LSTM-Att. (Proposed)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>RUL_Prediction</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>17.17974345574107</v>
+      </c>
+      <c r="G12" t="n">
+        <v>11.71968841552734</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.8162092566490173</v>
+      </c>
+      <c r="I12" t="n">
+        <v>822.2368774414062</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Reactive + Static</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Scheduling</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>-212.0747122140905</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1681.188977744547</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.7285</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Predictive Maintenance Only</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Scheduling</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="n">
+        <v>-128.4965696446448</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1777.765696446448</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.7788</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Scheduling Optimisation Only</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Scheduling</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>-46.00251542694358</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="L15" t="n">
+        <v>192.5209618911966</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="N15" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.7793</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
           <t>Proposed DRL-PPO (Integrated)</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>-136.0811558562774</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1872.611558562774</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Scheduling</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>-177.6384460471996</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2303.984460471996</v>
+      </c>
+      <c r="M16" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.7944</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/full_pipeline_results.xlsx
+++ b/outputs/full_pipeline_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,6 +497,21 @@
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>schedule_stability_index</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_maint_cost</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>automation_success_rate_%</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_latency_ms</t>
         </is>
       </c>
     </row>
@@ -530,6 +545,9 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -561,6 +579,9 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -592,6 +613,9 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -605,13 +629,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8685</v>
+        <v>0.8905</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3168831168831169</v>
+        <v>0.3577712609970675</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9541849348435026</v>
+        <v>0.9541773231031543</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -623,6 +647,9 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -636,13 +663,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.976</v>
+        <v>0.9755</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.6878980891719745</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9055839727195225</v>
+        <v>0.9073575082206795</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -654,6 +681,9 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -670,16 +700,16 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>13.19481293459313</v>
+        <v>13.43519238906723</v>
       </c>
       <c r="G7" t="n">
-        <v>10.14827346801758</v>
+        <v>10.44534683227539</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8915831446647644</v>
+        <v>0.8875969648361206</v>
       </c>
       <c r="I7" t="n">
-        <v>286.8256225585938</v>
+        <v>284.7279052734375</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -687,6 +717,9 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -703,16 +736,16 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>13.17457098651455</v>
+        <v>13.26077753471475</v>
       </c>
       <c r="G8" t="n">
-        <v>9.598400115966797</v>
+        <v>9.630173683166504</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8919155597686768</v>
+        <v>0.8904964327812195</v>
       </c>
       <c r="I8" t="n">
-        <v>310.8833312988281</v>
+        <v>324.8523864746094</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -720,6 +753,9 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -736,16 +772,16 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>13.38269335086335</v>
+        <v>12.8771858211665</v>
       </c>
       <c r="G9" t="n">
-        <v>9.862846374511719</v>
+        <v>9.597624778747559</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8884736895561218</v>
+        <v>0.8967399597167969</v>
       </c>
       <c r="I9" t="n">
-        <v>311.1583251953125</v>
+        <v>292.6030883789062</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -753,6 +789,9 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -769,16 +808,16 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>14.9528183541899</v>
+        <v>13.81256131119735</v>
       </c>
       <c r="G10" t="n">
-        <v>10.98691654205322</v>
+        <v>10.09186935424805</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8607688546180725</v>
+        <v>0.8811938762664795</v>
       </c>
       <c r="I10" t="n">
-        <v>553.6170043945312</v>
+        <v>405.5162353515625</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -786,6 +825,9 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -802,16 +844,16 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>18.27844028889039</v>
+        <v>17.82625650950244</v>
       </c>
       <c r="G11" t="n">
-        <v>12.46864891052246</v>
+        <v>13.0560131072998</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7919495701789856</v>
+        <v>0.8021160364151001</v>
       </c>
       <c r="I11" t="n">
-        <v>996.0452270507812</v>
+        <v>741.7400512695312</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -819,6 +861,9 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -835,16 +880,16 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>17.17974345574107</v>
+        <v>17.01786493808143</v>
       </c>
       <c r="G12" t="n">
-        <v>11.71968841552734</v>
+        <v>12.59199333190918</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8162092566490173</v>
+        <v>0.8196564912796021</v>
       </c>
       <c r="I12" t="n">
-        <v>822.2368774414062</v>
+        <v>623.0150756835938</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -852,6 +897,9 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -872,22 +920,31 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>-212.0747122140905</v>
+        <v>-208.505698354787</v>
       </c>
       <c r="K13" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="L13" t="n">
-        <v>1681.188977744547</v>
+        <v>1649.268098360283</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8</v>
+        <v>2.42</v>
       </c>
       <c r="N13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7285</v>
+        <v>0.7938</v>
+      </c>
+      <c r="P13" t="n">
+        <v>218</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>100</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.1278</v>
       </c>
     </row>
     <row r="14">
@@ -909,22 +966,31 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>-128.4965696446448</v>
+        <v>-116.708554315554</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="L14" t="n">
-        <v>1777.765696446448</v>
+        <v>1651.38554315554</v>
       </c>
       <c r="M14" t="n">
-        <v>1.6</v>
+        <v>2.08</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7788</v>
+        <v>0.7899</v>
+      </c>
+      <c r="P14" t="n">
+        <v>575.3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.1087</v>
       </c>
     </row>
     <row r="15">
@@ -946,22 +1012,31 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>-46.00251542694358</v>
+        <v>-46.72463697513484</v>
       </c>
       <c r="K15" t="n">
-        <v>4.29</v>
+        <v>4.36</v>
       </c>
       <c r="L15" t="n">
-        <v>192.5209618911966</v>
+        <v>192.7053081261236</v>
       </c>
       <c r="M15" t="n">
-        <v>2.76</v>
+        <v>3.52</v>
       </c>
       <c r="N15" t="n">
-        <v>8.58</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7793</v>
+        <v>0.7803</v>
+      </c>
+      <c r="P15" t="n">
+        <v>218</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>100</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.1083</v>
       </c>
     </row>
     <row r="16">
@@ -983,22 +1058,31 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>-177.6384460471996</v>
+        <v>-172.6710374216783</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="L16" t="n">
-        <v>2303.984460471996</v>
+        <v>2236.710374216782</v>
       </c>
       <c r="M16" t="n">
-        <v>8.76</v>
+        <v>9.76</v>
       </c>
       <c r="N16" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7944</v>
+        <v>0.7756</v>
+      </c>
+      <c r="P16" t="n">
+        <v>599.5</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>99.95999999999999</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.1663</v>
       </c>
     </row>
   </sheetData>
